--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104688_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104688_W26.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6739</v>
+        <v>5.3266</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2805</v>
+        <v>7.7194</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6067</v>
+        <v>-2.3927</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0205</v>
+        <v>7.013</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2279</v>
+        <v>2.2287</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7926</v>
+        <v>4.7843</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8189</v>
+        <v>7.7847</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L2" t="n">
-        <v>5.5575</v>
+        <v>5.5406</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7984</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4808</v>
+        <v>-0.8245</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9424</v>
+        <v>-0.7592</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6044</v>
+        <v>4.7661</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5945</v>
+        <v>2.7448</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0099</v>
+        <v>2.0213</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1381</v>
+        <v>4.1319</v>
       </c>
       <c r="H3" t="n">
-        <v>2.323</v>
+        <v>2.3317</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8151</v>
+        <v>1.8003</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1993</v>
+        <v>2.1611</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7202</v>
+        <v>0.71</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4791</v>
+        <v>1.4511</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9388</v>
+        <v>1.9708</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6028</v>
+        <v>1.6217</v>
       </c>
       <c r="O3" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0638</v>
+        <v>0.2197</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1512</v>
+        <v>0.039</v>
       </c>
       <c r="U3" t="n">
-        <v>0.215</v>
+        <v>0.1807</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5347</v>
+        <v>3.7635</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1238</v>
+        <v>1.8565</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4109</v>
+        <v>1.907</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5999</v>
+        <v>5.8949</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1196</v>
+        <v>3.6337</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5197000000000001</v>
+        <v>2.2612</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9702</v>
+        <v>4.886</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7836</v>
+        <v>2.8161</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866</v>
+        <v>2.0699</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6297</v>
+        <v>1.0088</v>
       </c>
       <c r="N4" t="n">
-        <v>1.336</v>
+        <v>0.8176</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7063</v>
+        <v>0.1912</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2278</v>
+        <v>0.1661</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2612</v>
+        <v>0.2271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9666</v>
+        <v>-0.0611</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2451</v>
+        <v>3.5237</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6811</v>
+        <v>0.5883</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5639999999999999</v>
+        <v>2.9354</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9752</v>
+        <v>2.6109</v>
       </c>
       <c r="H5" t="n">
-        <v>1.642</v>
+        <v>3.1246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3333</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9714</v>
+        <v>1.9616</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9741</v>
+        <v>1.7754</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0027</v>
+        <v>0.1862</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0038</v>
+        <v>0.6493</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3321</v>
+        <v>1.3492</v>
       </c>
       <c r="O5" t="n">
-        <v>0.336</v>
+        <v>-0.6998</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0449</v>
+        <v>1.2103</v>
       </c>
       <c r="T5" t="n">
-        <v>0.617</v>
+        <v>0.7453</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4279</v>
+        <v>0.465</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0043</v>
+        <v>3.2039</v>
       </c>
       <c r="E6" t="n">
-        <v>1.604</v>
+        <v>3.0765</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4003</v>
+        <v>0.1274</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9066</v>
+        <v>1.9897</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6436</v>
+        <v>1.6482</v>
       </c>
       <c r="I6" t="n">
-        <v>2.263</v>
+        <v>0.3415</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9274</v>
+        <v>1.9573</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8431</v>
+        <v>1.965</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0843</v>
+        <v>-0.0077</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8006</v>
+        <v>-0.3168</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1787</v>
+        <v>0.3492</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.015</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0297</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5278</v>
+        <v>-0.0447</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.892</v>
+        <v>1.0861</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.314</v>
+        <v>-0.0349</v>
       </c>
       <c r="F7" t="n">
-        <v>1.206</v>
+        <v>1.121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9007</v>
+        <v>2.9073</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3187</v>
+        <v>4.3223</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.418</v>
+        <v>-1.415</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1055</v>
+        <v>2.084</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8573</v>
+        <v>2.8441</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7952</v>
+        <v>0.8233</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4614</v>
+        <v>1.4782</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4035</v>
+        <v>0.5854</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1512</v>
+        <v>0.1574</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5547</v>
+        <v>0.428</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>G. NASPLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4255</v>
+        <v>-1.6488</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8029</v>
+        <v>-1.9143</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3774</v>
+        <v>0.2655</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4232</v>
+        <v>-0.7696</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1442</v>
+        <v>-0.7696</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.279</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4479</v>
+        <v>-0.7552</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.7552</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6127</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0247</v>
+        <v>-0.0144</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.0144</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6663</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6783</v>
+        <v>0.0313</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9134</v>
+        <v>-0.021</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7649</v>
+        <v>0.0523</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. NASPLER</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7932</v>
+        <v>-2.2319</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.025</v>
+        <v>-4.3558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2318</v>
+        <v>2.1239</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-2.4282</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.1491</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-2.2791</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7517</v>
+        <v>-2.4763</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7517</v>
+        <v>-0.8521</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.6242</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0159</v>
+        <v>0.0481</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0159</v>
+        <v>0.703</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1183</v>
+        <v>0.8792</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>0.3968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0209</v>
+        <v>0.4824</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1868</v>
+        <v>-3.4932</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2885</v>
+        <v>-3.0964</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8983</v>
+        <v>-0.3968</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6947</v>
+        <v>-4.7002</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6479</v>
+        <v>-1.6431</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0468</v>
+        <v>-3.0572</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.4668</v>
+        <v>-4.5038</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6145</v>
+        <v>-1.6277</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8523</v>
+        <v>-2.876</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.228</v>
+        <v>-0.1965</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0631</v>
+        <v>-0.3589</v>
       </c>
       <c r="T10" t="n">
-        <v>0.127</v>
+        <v>0.3665</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1901</v>
+        <v>-0.7254</v>
       </c>
       <c r="V10" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6697</v>
+        <v>-4.0685</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2315</v>
+        <v>-1.9027</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4382</v>
+        <v>-2.1657</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2242</v>
+        <v>-2.2274</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8701</v>
+        <v>-0.8702</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3541</v>
+        <v>-1.3572</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0625</v>
+        <v>-2.0858</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4125</v>
+        <v>-0.4244</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1617</v>
+        <v>-0.1416</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.194</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3297</v>
+        <v>0.0253</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.6176</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.879200000000001</v>
+        <v>10.2275</v>
       </c>
       <c r="E12" t="n">
-        <v>4.622</v>
+        <v>4.681399999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2571</v>
+        <v>5.546299999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>14.4313</v>
+        <v>14.4223</v>
       </c>
       <c r="H12" t="n">
-        <v>13.845</v>
+        <v>13.8572</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5864</v>
+        <v>0.5651999999999997</v>
       </c>
       <c r="J12" t="n">
-        <v>11.2638</v>
+        <v>11.0136</v>
       </c>
       <c r="K12" t="n">
-        <v>8.825800000000001</v>
+        <v>8.695200000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>2.438000000000001</v>
+        <v>2.318400000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1675</v>
+        <v>3.4085</v>
       </c>
       <c r="N12" t="n">
-        <v>5.0192</v>
+        <v>5.161899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8517</v>
+        <v>-1.7531</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9526999999999997</v>
+        <v>1.3014</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5275</v>
+        <v>1.9008</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5746999999999999</v>
+        <v>-0.5996000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.370799999999999</v>
+        <v>-4.357800000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>4.3064</v>
+        <v>4.2865</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.677099999999999</v>
+        <v>-8.644299999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3465</v>
+        <v>3.5105</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9023</v>
+        <v>3.6845</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5558</v>
+        <v>-0.174</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0459</v>
+        <v>2.0451</v>
       </c>
       <c r="H13" t="n">
-        <v>1.462</v>
+        <v>1.4456</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5839</v>
+        <v>0.5995</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4311</v>
+        <v>2.3995</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2818</v>
+        <v>2.2506</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3852</v>
+        <v>-0.3544</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3668</v>
+        <v>0.5353</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0325</v>
+        <v>0.8589</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6657</v>
+        <v>-0.3235</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5405</v>
+        <v>2.47</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3596</v>
+        <v>3.0123</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1809</v>
+        <v>-0.5423</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6113</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0623</v>
+        <v>-0.9052</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.549</v>
+        <v>0.8424</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0639</v>
+        <v>2.0838</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1039</v>
+        <v>0.4169</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.04</v>
+        <v>1.6669</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6752</v>
+        <v>-2.1466</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1662</v>
+        <v>-1.3221</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.509</v>
+        <v>-0.8245</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>1.218</v>
+        <v>-0.2592</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1765</v>
+        <v>-0.0424</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0414</v>
+        <v>-0.2168</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>2.3367</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>2.3367</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4411</v>
+        <v>1.5283</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6538</v>
+        <v>-0.2225</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0949</v>
+        <v>1.7508</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1166</v>
+        <v>0.1066</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1993</v>
+        <v>0.1901</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0835</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4763</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6887</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5929</v>
+        <v>0.6192</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9024</v>
+        <v>-0.806</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0434</v>
+        <v>-0.5718</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.859</v>
+        <v>-0.2342</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3161</v>
+        <v>0.7517</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6504</v>
+        <v>0.2856</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3344</v>
+        <v>0.4662</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0554</v>
+        <v>-1.5882</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9135</v>
+        <v>-1.0463</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8582</v>
+        <v>-0.5419</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1261</v>
+        <v>0.0585</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4258</v>
+        <v>0.1034</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7003</v>
+        <v>-0.0449</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1815</v>
+        <v>-1.6467</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3393</v>
+        <v>-1.1497</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.497</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.4283</v>
+        <v>0.4098</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4608</v>
+        <v>0.118</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9675</v>
+        <v>0.2919</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3461</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3461</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5978</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6542</v>
+        <v>-1.1959</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0564</v>
+        <v>1.1147</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9811</v>
+        <v>-1.9748</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8932</v>
+        <v>-1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.0513</v>
+        <v>-2.0621</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0701</v>
+        <v>0.0873</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.522</v>
+        <v>-0.0185</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6956</v>
+        <v>-0.2232</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1736</v>
+        <v>0.2047</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3559</v>
+        <v>-0.8398</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0076</v>
+        <v>-0.6566</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3483</v>
+        <v>-0.1832</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.182</v>
+        <v>-1.1777</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0202</v>
+        <v>0.0228</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2021</v>
+        <v>-1.2006</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6635</v>
       </c>
       <c r="K18" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5222</v>
+        <v>-0.5143</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4007</v>
+        <v>0.1103</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.419</v>
+        <v>-1.6247</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5986</v>
+        <v>-1.7499</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1796</v>
+        <v>0.1252</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8898</v>
+        <v>-0.8895</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9134</v>
+        <v>-1.9128</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0236</v>
+        <v>1.0234</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4887</v>
+        <v>-0.5206</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0776</v>
+        <v>-1.0934</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4011</v>
+        <v>-0.3689</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3366</v>
+        <v>0.1266</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2511</v>
+        <v>0.1365</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0856</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3556</v>
+        <v>-3.0923</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0163</v>
+        <v>-0.0113</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3719</v>
+        <v>-3.0809</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.688</v>
+        <v>-2.6866</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4616</v>
+        <v>-2.4696</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2265</v>
+        <v>-0.2171</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0775</v>
+        <v>-0.1083</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6345</v>
+        <v>-0.6592</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6106</v>
+        <v>-2.5783</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.827</v>
+        <v>-1.8103</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.291</v>
+        <v>0.5457</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3206</v>
+        <v>0.3246</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0297</v>
+        <v>0.2211</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1403</v>
+        <v>-3.7093</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4819</v>
+        <v>-3.2577</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6584</v>
+        <v>-0.4516</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.906</v>
+        <v>-2.8974</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3117</v>
+        <v>-2.3093</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5944</v>
+        <v>-0.5881</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4434</v>
+        <v>-1.4503</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4626</v>
+        <v>-1.4471</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7806</v>
+        <v>-0.3567</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9043</v>
+        <v>-0.6692</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1237</v>
+        <v>0.3126</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6546</v>
+        <v>-6.4234</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7895</v>
+        <v>-5.4347</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8651</v>
+        <v>-0.9888</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.28</v>
+        <v>-5.297</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.9708</v>
+        <v>-4.9824</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3092</v>
+        <v>-0.3145</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5917</v>
+        <v>-2.633</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.8523</v>
+        <v>-3.876</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2607</v>
+        <v>1.243</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6884</v>
+        <v>-2.664</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8691</v>
+        <v>1.1287</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2461</v>
+        <v>0.6614</v>
       </c>
       <c r="U22" t="n">
-        <v>0.623</v>
+        <v>0.4672</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.879</v>
+        <v>-7.510199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.257</v>
+        <v>-5.546200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6221</v>
+        <v>-1.9639</v>
       </c>
       <c r="G23" t="n">
-        <v>-14.4311</v>
+        <v>-14.4222</v>
       </c>
       <c r="H23" t="n">
-        <v>-13.845</v>
+        <v>-13.8571</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5860000000000001</v>
+        <v>-0.5651999999999998</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1676</v>
+        <v>-3.4086</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.0191</v>
+        <v>-5.161799999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8518</v>
+        <v>1.7533</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.2638</v>
+        <v>-11.0138</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.825700000000001</v>
+        <v>-8.6951</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.438</v>
+        <v>-2.3185</v>
       </c>
       <c r="P23" t="n">
-        <v>1.134100000000001</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-11.3417</v>
+        <v>-11.3816</v>
       </c>
       <c r="R23" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9525000000000001</v>
+        <v>1.416</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5749000000000004</v>
+        <v>0.5996</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5275</v>
+        <v>0.8166</v>
       </c>
       <c r="V23" t="n">
-        <v>4.3708</v>
+        <v>4.3578</v>
       </c>
       <c r="W23" t="n">
-        <v>8.677299999999999</v>
+        <v>8.644400000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.306500000000001</v>
+        <v>-4.2865</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104688_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104688_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.644299999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104688_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-4.2865</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
